--- a/AAII_Financials/Yearly/META_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/META_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,149 +656,161 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="8" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>134902000</v>
+      </c>
+      <c r="E8" s="3">
         <v>116609000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>117929000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>85965000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>70697000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>55838000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>40653000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>27638000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>17928000</v>
       </c>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>26006000</v>
+      </c>
+      <c r="E9" s="3">
         <v>23754000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>22649000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>16692000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>12770000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>9355000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>5454000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3789000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2867000</v>
       </c>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>108896000</v>
+      </c>
+      <c r="E10" s="3">
         <v>92855000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>95280000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>69273000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>57927000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>46483000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>35199000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>23849000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>15061000</v>
       </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -811,38 +823,42 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>36911000</v>
+      </c>
+      <c r="E12" s="3">
         <v>33619000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>24655000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>18447000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>13600000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>10273000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>7754000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>5919000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>4816000</v>
       </c>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -870,26 +886,29 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>2255000</v>
+      </c>
+      <c r="E14" s="3">
         <v>4611000</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="3">
         <v>5000000</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>10</v>
@@ -900,9 +919,12 @@
       <c r="K14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -930,9 +952,12 @@
       <c r="K15" s="3">
         <v>0</v>
       </c>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -942,68 +967,75 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>88151000</v>
+      </c>
+      <c r="E17" s="3">
         <v>87665000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>71176000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>53294000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>46711000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>30925000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>20450000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>15211000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>11703000</v>
       </c>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>46751000</v>
+      </c>
+      <c r="E18" s="3">
         <v>28944000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>46753000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>32671000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>23986000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>24913000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>20203000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>12427000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>6225000</v>
       </c>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1016,73 +1048,80 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1123000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-125000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>531000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>509000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>846000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>457000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>397000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>101000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-8000</v>
       </c>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>59052000</v>
+      </c>
+      <c r="E21" s="3">
         <v>37505000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>55251000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>40042000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>30573000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>29685000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>23625000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>14870000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>8162000</v>
       </c>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>10</v>
+      <c r="D22" s="3">
+        <v>446000</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>10</v>
@@ -1090,84 +1129,93 @@
       <c r="F22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G22" s="3">
+      <c r="G22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H22" s="3">
         <v>20000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>9000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>6000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>10000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>23000</v>
       </c>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>47428000</v>
+      </c>
+      <c r="E23" s="3">
         <v>28819000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>47284000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>33180000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>24812000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>25361000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>20594000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>12518000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>6194000</v>
       </c>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>7190000</v>
+      </c>
+      <c r="E24" s="3">
         <v>4109000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>7914000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4034000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>6327000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3249000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2387000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2301000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2506000</v>
       </c>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1195,69 +1243,78 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-      <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>40238000</v>
+      </c>
+      <c r="E26" s="3">
         <v>24710000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>39370000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>29146000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>18485000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>22112000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>18207000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>10217000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3688000</v>
       </c>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>40238000</v>
+      </c>
+      <c r="E27" s="3">
         <v>24710000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>39370000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>29146000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>18485000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>22111000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>18193000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>10188000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3669000</v>
       </c>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1285,17 +1342,20 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-      <c r="L28" s="3"/>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-1140000</v>
+      </c>
+      <c r="E29" s="3">
         <v>-1510000</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>10</v>
@@ -1306,18 +1366,21 @@
       <c r="H29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I29" s="3">
+      <c r="I29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J29" s="3">
         <v>-2273000</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L29" s="3"/>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1345,9 +1408,12 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-      <c r="L30" s="3"/>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1375,69 +1441,78 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-      <c r="L31" s="3"/>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1123000</v>
+      </c>
+      <c r="E32" s="3">
         <v>125000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-531000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-509000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-846000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-457000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-397000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-101000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>8000</v>
       </c>
-      <c r="L32" s="3"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>39098000</v>
+      </c>
+      <c r="E33" s="3">
         <v>23200000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>39370000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>29146000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>18485000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>22111000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>15920000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>10188000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3669000</v>
       </c>
-      <c r="L33" s="3"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1465,74 +1540,83 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-      <c r="L34" s="3"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>39098000</v>
+      </c>
+      <c r="E35" s="3">
         <v>23200000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>39370000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>29146000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>18485000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>22111000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>15920000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>10188000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3669000</v>
       </c>
-      <c r="L35" s="3"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1545,8 +1629,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1559,98 +1644,108 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>41862000</v>
+      </c>
+      <c r="E41" s="3">
         <v>14681000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>16601000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>17576000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>19079000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>10019000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8079000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>8903000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4907000</v>
       </c>
-      <c r="L41" s="3"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>23541000</v>
+      </c>
+      <c r="E42" s="3">
         <v>26057000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>31397000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>44378000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>35776000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>31095000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>33632000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>20546000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>13527000</v>
       </c>
-      <c r="L42" s="3"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>16169000</v>
+      </c>
+      <c r="E43" s="3">
         <v>13466000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>14039000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>11335000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>9518000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7587000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5832000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3993000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2559000</v>
       </c>
-      <c r="L43" s="3"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1678,86 +1773,95 @@
       <c r="K44" s="3">
         <v>0</v>
       </c>
-      <c r="L44" s="3"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L44" s="3">
+        <v>0</v>
+      </c>
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3793000</v>
+      </c>
+      <c r="E45" s="3">
         <v>5345000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4629000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2381000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1852000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1779000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1020000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>959000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>659000</v>
       </c>
-      <c r="L45" s="3"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>85365000</v>
+      </c>
+      <c r="E46" s="3">
         <v>59549000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>66666000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>75670000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>66225000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>50480000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>48563000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>34401000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>21652000</v>
       </c>
-      <c r="L46" s="3"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>6141000</v>
+      </c>
+      <c r="E47" s="3">
         <v>6201000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>6775000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>6234000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>86000</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>10</v>
@@ -1768,69 +1872,78 @@
       <c r="K47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L47" s="3"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>109881000</v>
+      </c>
+      <c r="E48" s="3">
         <v>92191000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>69964000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>54981000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>44783000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>24683000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>13721000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8591000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5687000</v>
       </c>
-      <c r="L48" s="3"/>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>21442000</v>
+      </c>
+      <c r="E49" s="3">
         <v>21203000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>19831000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>19673000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>19609000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>19595000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>20105000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>20657000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>21272000</v>
       </c>
-      <c r="L49" s="3"/>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1858,9 +1971,12 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-      <c r="L50" s="3"/>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1888,39 +2004,45 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-      <c r="L51" s="3"/>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6794000</v>
+      </c>
+      <c r="E52" s="3">
         <v>6583000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2751000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2758000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2673000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2576000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2135000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1312000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>796000</v>
       </c>
-      <c r="L52" s="3"/>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1948,39 +2070,45 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-      <c r="L53" s="3"/>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>229623000</v>
+      </c>
+      <c r="E54" s="3">
         <v>185727000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>165987000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>159316000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>133376000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>97334000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>84524000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>64961000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>49407000</v>
       </c>
-      <c r="L54" s="3"/>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1993,8 +2121,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2007,146 +2136,159 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5712000</v>
+      </c>
+      <c r="E57" s="3">
         <v>6107000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5135000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2424000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2249000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1361000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>770000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>582000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>413000</v>
       </c>
-      <c r="L57" s="3"/>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>90000</v>
+      </c>
+      <c r="E58" s="3">
         <v>129000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>75000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>54000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>55000</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
-      <c r="I58" s="3" t="s">
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>208000</v>
       </c>
-      <c r="L58" s="3"/>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>26158000</v>
+      </c>
+      <c r="E59" s="3">
         <v>20790000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>15925000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>12503000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>12749000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5656000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2990000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2293000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1304000</v>
       </c>
-      <c r="L59" s="3"/>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>31960000</v>
+      </c>
+      <c r="E60" s="3">
         <v>27026000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>21135000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>14981000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>15053000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7017000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3760000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2875000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1925000</v>
       </c>
-      <c r="L60" s="3"/>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>18985000</v>
+      </c>
+      <c r="E61" s="3">
         <v>10481000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>506000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>469000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>418000</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
@@ -2154,41 +2296,47 @@
         <v>0</v>
       </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>107000</v>
       </c>
-      <c r="L61" s="3"/>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>25510000</v>
+      </c>
+      <c r="E62" s="3">
         <v>22507000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>19467000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>15576000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>16851000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>6190000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>6417000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2892000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3157000</v>
       </c>
-      <c r="L62" s="3"/>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2216,9 +2364,12 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-      <c r="L63" s="3"/>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2246,9 +2397,12 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-      <c r="L64" s="3"/>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2276,39 +2430,45 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-      <c r="L65" s="3"/>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>76455000</v>
+      </c>
+      <c r="E66" s="3">
         <v>60014000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>41108000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>31026000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>32322000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>13207000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>10177000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5767000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5189000</v>
       </c>
-      <c r="L66" s="3"/>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2321,8 +2481,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2350,9 +2511,12 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-      <c r="L68" s="3"/>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2380,9 +2544,12 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-      <c r="L69" s="3"/>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2410,9 +2577,12 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-      <c r="L70" s="3"/>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2440,39 +2610,45 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-      <c r="L71" s="3"/>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>82070000</v>
+      </c>
+      <c r="E72" s="3">
         <v>64799000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>69761000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>77345000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>55692000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>41981000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>33990000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>21670000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>9787000</v>
       </c>
-      <c r="L72" s="3"/>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2500,9 +2676,12 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-      <c r="L73" s="3"/>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2530,9 +2709,12 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-      <c r="L74" s="3"/>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2560,39 +2742,45 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-      <c r="L75" s="3"/>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>153168000</v>
+      </c>
+      <c r="E76" s="3">
         <v>125713000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>124879000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>128290000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>101054000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>84127000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>74347000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>59194000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>44218000</v>
       </c>
-      <c r="L76" s="3"/>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2620,74 +2808,83 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-      <c r="L77" s="3"/>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2"/>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M80" s="2"/>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>39098000</v>
+      </c>
+      <c r="E81" s="3">
         <v>23200000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>39370000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>29146000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>18485000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>22111000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>15920000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>10188000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3669000</v>
       </c>
-      <c r="L81" s="3"/>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2700,38 +2897,42 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>11178000</v>
+      </c>
+      <c r="E83" s="3">
         <v>8686000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>7967000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>6862000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5741000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4315000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3025000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2342000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1945000</v>
       </c>
-      <c r="L83" s="3"/>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2759,9 +2960,12 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-      <c r="L84" s="3"/>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2789,9 +2993,12 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-      <c r="L85" s="3"/>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2819,9 +3026,12 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-      <c r="L86" s="3"/>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2849,9 +3059,12 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-      <c r="L87" s="3"/>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2879,39 +3092,45 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-      <c r="L88" s="3"/>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>71113000</v>
+      </c>
+      <c r="E89" s="3">
         <v>50475000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>57683000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>38747000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>36314000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>29274000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>24216000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>16108000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>10320000</v>
       </c>
-      <c r="L89" s="3"/>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2924,38 +3143,42 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-27266000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-31431000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-18567000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-15115000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-15102000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-13915000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-6733000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4491000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2523000</v>
       </c>
-      <c r="L91" s="3"/>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2983,9 +3206,12 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-      <c r="L92" s="3"/>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3013,39 +3239,45 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-      <c r="L93" s="3"/>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-24495000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-28970000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-7570000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-30059000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-19864000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-11603000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-20118000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-11792000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-9434000</v>
       </c>
-      <c r="L94" s="3"/>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3058,8 +3290,9 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3087,9 +3320,12 @@
       <c r="K96" s="3">
         <v>0</v>
       </c>
-      <c r="L96" s="3"/>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3117,9 +3353,12 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-      <c r="L97" s="3"/>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3147,9 +3386,12 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-      <c r="L98" s="3"/>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3177,97 +3419,109 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-      <c r="L99" s="3"/>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-19500000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-22136000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-50728000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-10292000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-7299000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-15572000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-5235000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-310000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-139000</v>
       </c>
-      <c r="L100" s="3"/>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>113000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-638000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-474000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>279000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>4000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-179000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>232000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-63000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-155000</v>
       </c>
-      <c r="L101" s="3"/>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>27231000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1269000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1089000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1325000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>9155000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1920000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-905000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3943000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>592000</v>
       </c>
-      <c r="L102" s="3"/>
+      <c r="M102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/META_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/META_YR_FIN.xlsx
@@ -830,7 +830,7 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>36911000</v>
+        <v>36489000</v>
       </c>
       <c r="E12" s="3">
         <v>33619000</v>
@@ -896,7 +896,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>2255000</v>
+        <v>3452000</v>
       </c>
       <c r="E14" s="3">
         <v>4611000</v>
@@ -1187,10 +1187,10 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>7190000</v>
+        <v>7755000</v>
       </c>
       <c r="E24" s="3">
-        <v>4109000</v>
+        <v>5258000</v>
       </c>
       <c r="F24" s="3">
         <v>7914000</v>
@@ -1253,10 +1253,10 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>40238000</v>
+        <v>39673000</v>
       </c>
       <c r="E26" s="3">
-        <v>24710000</v>
+        <v>23561000</v>
       </c>
       <c r="F26" s="3">
         <v>39370000</v>
@@ -1286,10 +1286,10 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>40238000</v>
+        <v>39673000</v>
       </c>
       <c r="E27" s="3">
-        <v>24710000</v>
+        <v>23561000</v>
       </c>
       <c r="F27" s="3">
         <v>39370000</v>
@@ -1352,10 +1352,10 @@
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>-1140000</v>
+        <v>-575000</v>
       </c>
       <c r="E29" s="3">
-        <v>-1510000</v>
+        <v>-361000</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>10</v>

--- a/AAII_Financials/Yearly/META_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/META_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="92">
   <si>
     <t>META</t>
   </si>
@@ -896,10 +896,10 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>3452000</v>
+        <v>3553000</v>
       </c>
       <c r="E14" s="3">
-        <v>4611000</v>
+        <v>5058000</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>10</v>
@@ -929,25 +929,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>11178000</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>8686000</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>7967000</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>6862000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>5741000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>4315000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>3025000</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -974,10 +974,10 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>88151000</v>
+        <v>84699000</v>
       </c>
       <c r="E17" s="3">
-        <v>87665000</v>
+        <v>83054000</v>
       </c>
       <c r="F17" s="3">
         <v>71176000</v>
@@ -986,7 +986,7 @@
         <v>53294000</v>
       </c>
       <c r="H17" s="3">
-        <v>46711000</v>
+        <v>41711000</v>
       </c>
       <c r="I17" s="3">
         <v>30925000</v>
@@ -1007,10 +1007,10 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>46751000</v>
+        <v>50203000</v>
       </c>
       <c r="E18" s="3">
-        <v>28944000</v>
+        <v>33555000</v>
       </c>
       <c r="F18" s="3">
         <v>46753000</v>
@@ -1019,7 +1019,7 @@
         <v>32671000</v>
       </c>
       <c r="H18" s="3">
-        <v>23986000</v>
+        <v>28986000</v>
       </c>
       <c r="I18" s="3">
         <v>24913000</v>
@@ -1055,25 +1055,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1123000</v>
+        <v>415000</v>
       </c>
       <c r="E20" s="3">
-        <v>-125000</v>
+        <v>-46000</v>
       </c>
       <c r="F20" s="3">
-        <v>531000</v>
+        <v>-70000</v>
       </c>
       <c r="G20" s="3">
-        <v>509000</v>
+        <v>163000</v>
       </c>
       <c r="H20" s="3">
-        <v>846000</v>
+        <v>78000</v>
       </c>
       <c r="I20" s="3">
-        <v>457000</v>
+        <v>204000</v>
       </c>
       <c r="J20" s="3">
-        <v>397000</v>
+        <v>1000</v>
       </c>
       <c r="K20" s="3">
         <v>101000</v>
@@ -1088,25 +1088,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>59052000</v>
+        <v>60966000</v>
       </c>
       <c r="E21" s="3">
-        <v>37505000</v>
+        <v>42287000</v>
       </c>
       <c r="F21" s="3">
-        <v>55251000</v>
+        <v>54790000</v>
       </c>
       <c r="G21" s="3">
-        <v>40042000</v>
+        <v>39370000</v>
       </c>
       <c r="H21" s="3">
-        <v>30573000</v>
+        <v>34649000</v>
       </c>
       <c r="I21" s="3">
-        <v>29685000</v>
+        <v>29024000</v>
       </c>
       <c r="J21" s="3">
-        <v>23625000</v>
+        <v>23227000</v>
       </c>
       <c r="K21" s="3">
         <v>14870000</v>
@@ -1123,20 +1123,20 @@
       <c r="D22" s="3">
         <v>446000</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>10</v>
+      <c r="E22" s="3">
+        <v>185000</v>
+      </c>
+      <c r="F22" s="3">
+        <v>23000</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H22" s="3">
-        <v>20000</v>
-      </c>
-      <c r="I22" s="3">
-        <v>9000</v>
+      <c r="H22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="J22" s="3">
         <v>6000</v>
@@ -1187,10 +1187,10 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>7755000</v>
+        <v>8330000</v>
       </c>
       <c r="E24" s="3">
-        <v>5258000</v>
+        <v>5619000</v>
       </c>
       <c r="F24" s="3">
         <v>7914000</v>
@@ -1205,7 +1205,7 @@
         <v>3249000</v>
       </c>
       <c r="J24" s="3">
-        <v>2387000</v>
+        <v>4660000</v>
       </c>
       <c r="K24" s="3">
         <v>2301000</v>
@@ -1253,10 +1253,10 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>39673000</v>
+        <v>39098000</v>
       </c>
       <c r="E26" s="3">
-        <v>23561000</v>
+        <v>23200000</v>
       </c>
       <c r="F26" s="3">
         <v>39370000</v>
@@ -1271,7 +1271,7 @@
         <v>22112000</v>
       </c>
       <c r="J26" s="3">
-        <v>18207000</v>
+        <v>15934000</v>
       </c>
       <c r="K26" s="3">
         <v>10217000</v>
@@ -1286,10 +1286,10 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>39673000</v>
+        <v>39098000</v>
       </c>
       <c r="E27" s="3">
-        <v>23561000</v>
+        <v>23200000</v>
       </c>
       <c r="F27" s="3">
         <v>39370000</v>
@@ -1304,7 +1304,7 @@
         <v>22111000</v>
       </c>
       <c r="J27" s="3">
-        <v>18193000</v>
+        <v>15920000</v>
       </c>
       <c r="K27" s="3">
         <v>10188000</v>
@@ -1352,25 +1352,25 @@
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>-575000</v>
+        <v>0</v>
       </c>
       <c r="E29" s="3">
-        <v>-361000</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>10</v>
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>-2273000</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>10</v>
@@ -1451,25 +1451,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1123000</v>
+        <v>-415000</v>
       </c>
       <c r="E32" s="3">
-        <v>125000</v>
+        <v>46000</v>
       </c>
       <c r="F32" s="3">
-        <v>-531000</v>
+        <v>70000</v>
       </c>
       <c r="G32" s="3">
-        <v>-509000</v>
+        <v>-163000</v>
       </c>
       <c r="H32" s="3">
-        <v>-846000</v>
+        <v>-78000</v>
       </c>
       <c r="I32" s="3">
-        <v>-457000</v>
+        <v>-204000</v>
       </c>
       <c r="J32" s="3">
-        <v>-397000</v>
+        <v>-1000</v>
       </c>
       <c r="K32" s="3">
         <v>-101000</v>
@@ -1499,10 +1499,10 @@
         <v>18485000</v>
       </c>
       <c r="I33" s="3">
-        <v>22111000</v>
+        <v>22112000</v>
       </c>
       <c r="J33" s="3">
-        <v>15920000</v>
+        <v>15934000</v>
       </c>
       <c r="K33" s="3">
         <v>10188000</v>
@@ -1565,10 +1565,10 @@
         <v>18485000</v>
       </c>
       <c r="I35" s="3">
-        <v>22111000</v>
+        <v>22112000</v>
       </c>
       <c r="J35" s="3">
-        <v>15920000</v>
+        <v>15934000</v>
       </c>
       <c r="K35" s="3">
         <v>10188000</v>
@@ -1749,26 +1749,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -1782,26 +1782,26 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>3793000</v>
-      </c>
-      <c r="E45" s="3">
-        <v>5345000</v>
-      </c>
-      <c r="F45" s="3">
-        <v>4629000</v>
-      </c>
-      <c r="G45" s="3">
-        <v>2381000</v>
-      </c>
-      <c r="H45" s="3">
-        <v>1852000</v>
-      </c>
-      <c r="I45" s="3">
-        <v>1779000</v>
-      </c>
-      <c r="J45" s="3">
-        <v>1020000</v>
+      <c r="D45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K45" s="3">
         <v>959000</v>
@@ -2143,25 +2143,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>5712000</v>
+        <v>4849000</v>
       </c>
       <c r="E57" s="3">
-        <v>6107000</v>
+        <v>4990000</v>
       </c>
       <c r="F57" s="3">
-        <v>5135000</v>
+        <v>4083000</v>
       </c>
       <c r="G57" s="3">
-        <v>2424000</v>
+        <v>1331000</v>
       </c>
       <c r="H57" s="3">
-        <v>2249000</v>
+        <v>1363000</v>
       </c>
       <c r="I57" s="3">
-        <v>1361000</v>
+        <v>820000</v>
       </c>
       <c r="J57" s="3">
-        <v>770000</v>
+        <v>380000</v>
       </c>
       <c r="K57" s="3">
         <v>582000</v>
@@ -2176,25 +2176,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>90000</v>
+        <v>1713000</v>
       </c>
       <c r="E58" s="3">
-        <v>129000</v>
+        <v>1367000</v>
       </c>
       <c r="F58" s="3">
-        <v>75000</v>
+        <v>1127000</v>
       </c>
       <c r="G58" s="3">
-        <v>54000</v>
+        <v>1023000</v>
       </c>
       <c r="H58" s="3">
-        <v>55000</v>
+        <v>800000</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>10</v>
+        <v>500000</v>
+      </c>
+      <c r="J58" s="3">
+        <v>0</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2209,25 +2209,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>26158000</v>
+        <v>18739000</v>
       </c>
       <c r="E59" s="3">
-        <v>20790000</v>
+        <v>16078000</v>
       </c>
       <c r="F59" s="3">
-        <v>15925000</v>
+        <v>12773000</v>
       </c>
       <c r="G59" s="3">
-        <v>12503000</v>
+        <v>10018000</v>
       </c>
       <c r="H59" s="3">
-        <v>12749000</v>
+        <v>11186000</v>
       </c>
       <c r="I59" s="3">
-        <v>5656000</v>
+        <v>4494000</v>
       </c>
       <c r="J59" s="3">
-        <v>2990000</v>
+        <v>2590000</v>
       </c>
       <c r="K59" s="3">
         <v>2293000</v>
@@ -2275,19 +2275,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>18985000</v>
+        <v>36211000</v>
       </c>
       <c r="E61" s="3">
-        <v>10481000</v>
+        <v>25224000</v>
       </c>
       <c r="F61" s="3">
-        <v>506000</v>
+        <v>12746000</v>
       </c>
       <c r="G61" s="3">
-        <v>469000</v>
+        <v>9631000</v>
       </c>
       <c r="H61" s="3">
-        <v>418000</v>
+        <v>9524000</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
@@ -2308,25 +2308,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>25510000</v>
+        <v>8284000</v>
       </c>
       <c r="E62" s="3">
-        <v>22507000</v>
+        <v>7764000</v>
       </c>
       <c r="F62" s="3">
-        <v>19467000</v>
+        <v>7227000</v>
       </c>
       <c r="G62" s="3">
-        <v>15576000</v>
+        <v>6414000</v>
       </c>
       <c r="H62" s="3">
-        <v>16851000</v>
+        <v>7745000</v>
       </c>
       <c r="I62" s="3">
-        <v>6190000</v>
+        <v>5517000</v>
       </c>
       <c r="J62" s="3">
-        <v>6417000</v>
+        <v>6367000</v>
       </c>
       <c r="K62" s="3">
         <v>2892000</v>
@@ -2871,10 +2871,10 @@
         <v>18485000</v>
       </c>
       <c r="I81" s="3">
-        <v>22111000</v>
+        <v>22112000</v>
       </c>
       <c r="J81" s="3">
-        <v>15920000</v>
+        <v>15934000</v>
       </c>
       <c r="K81" s="3">
         <v>10188000</v>
@@ -2904,25 +2904,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>11178000</v>
+        <v>11017000</v>
       </c>
       <c r="E83" s="3">
-        <v>8686000</v>
+        <v>8501000</v>
       </c>
       <c r="F83" s="3">
-        <v>7967000</v>
+        <v>7560000</v>
       </c>
       <c r="G83" s="3">
-        <v>6862000</v>
+        <v>6389000</v>
       </c>
       <c r="H83" s="3">
-        <v>5741000</v>
+        <v>5179000</v>
       </c>
       <c r="I83" s="3">
-        <v>4315000</v>
+        <v>3675000</v>
       </c>
       <c r="J83" s="3">
-        <v>3025000</v>
+        <v>2333000</v>
       </c>
       <c r="K83" s="3">
         <v>2342000</v>
@@ -3156,10 +3156,10 @@
         <v>-31431000</v>
       </c>
       <c r="F91" s="3">
-        <v>-18567000</v>
+        <v>-18690000</v>
       </c>
       <c r="G91" s="3">
-        <v>-15115000</v>
+        <v>-15163000</v>
       </c>
       <c r="H91" s="3">
         <v>-15102000</v>

--- a/AAII_Financials/Yearly/META_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/META_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
   <si>
     <t>META</t>
   </si>
@@ -656,161 +656,173 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>164501000</v>
+      </c>
+      <c r="E8" s="3">
         <v>134902000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>116609000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>117929000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>85965000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>70697000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>55838000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>40653000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>27638000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>17928000</v>
       </c>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>30130000</v>
+      </c>
+      <c r="E9" s="3">
         <v>26006000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>23754000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>22649000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>16692000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>12770000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>9355000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>5454000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3789000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2867000</v>
       </c>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>134371000</v>
+      </c>
+      <c r="E10" s="3">
         <v>108896000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>92855000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>95280000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>69273000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>57927000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>46483000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>35199000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>23849000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>15061000</v>
       </c>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -824,41 +836,45 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>36489000</v>
+        <v>43619000</v>
       </c>
       <c r="E12" s="3">
+        <v>36911000</v>
+      </c>
+      <c r="F12" s="3">
         <v>33619000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>24655000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>18447000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>13600000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>10273000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>7754000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>5919000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>4816000</v>
       </c>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -889,29 +905,32 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>3553000</v>
+        <v>-1119000</v>
       </c>
       <c r="E14" s="3">
+        <v>2356000</v>
+      </c>
+      <c r="F14" s="3">
         <v>5058000</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I14" s="3">
         <v>5000000</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>10</v>
@@ -922,42 +941,48 @@
       <c r="L14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M14" s="3"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>15498000</v>
+      </c>
+      <c r="E15" s="3">
         <v>11178000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>8686000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>7967000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>6862000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>5741000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>4315000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3025000</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -968,74 +993,81 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>84699000</v>
+        <v>96282000</v>
       </c>
       <c r="E17" s="3">
+        <v>85896000</v>
+      </c>
+      <c r="F17" s="3">
         <v>83054000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>71176000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>53294000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>41711000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>30925000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>20450000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>15211000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>11703000</v>
       </c>
-      <c r="M17" s="3"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>50203000</v>
+        <v>68219000</v>
       </c>
       <c r="E18" s="3">
+        <v>49006000</v>
+      </c>
+      <c r="F18" s="3">
         <v>33555000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>46753000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>32671000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>28986000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>24913000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>20203000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>12427000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>6225000</v>
       </c>
-      <c r="M18" s="3"/>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1049,88 +1081,95 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>477000</v>
+      </c>
+      <c r="E20" s="3">
         <v>415000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-46000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-70000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>163000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>78000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>204000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>101000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-8000</v>
       </c>
-      <c r="M20" s="3"/>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>60966000</v>
+        <v>83240000</v>
       </c>
       <c r="E21" s="3">
+        <v>59769000</v>
+      </c>
+      <c r="F21" s="3">
         <v>42287000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>54790000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>39370000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>34649000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>29024000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>23227000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>14870000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>8162000</v>
       </c>
-      <c r="M21" s="3"/>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>715000</v>
+      </c>
+      <c r="E22" s="3">
         <v>446000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>185000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>23000</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>10</v>
@@ -1138,84 +1177,93 @@
       <c r="I22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J22" s="3">
+      <c r="J22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K22" s="3">
         <v>6000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>10000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>23000</v>
       </c>
-      <c r="M22" s="3"/>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3"/>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>70663000</v>
+      </c>
+      <c r="E23" s="3">
         <v>47428000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>28819000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>47284000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>33180000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>24812000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>25361000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>20594000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>12518000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>6194000</v>
       </c>
-      <c r="M23" s="3"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>8303000</v>
+      </c>
+      <c r="E24" s="3">
         <v>8330000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5619000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7914000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4034000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>6327000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3249000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4660000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2301000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2506000</v>
       </c>
-      <c r="M24" s="3"/>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1246,75 +1294,84 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-      <c r="M25" s="3"/>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>62360000</v>
+      </c>
+      <c r="E26" s="3">
         <v>39098000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>23200000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>39370000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>29146000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>18485000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>22112000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>15934000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>10217000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3688000</v>
       </c>
-      <c r="M26" s="3"/>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>62360000</v>
+      </c>
+      <c r="E27" s="3">
         <v>39098000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>23200000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>39370000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>29146000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>18485000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>22111000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>15920000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>10188000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3669000</v>
       </c>
-      <c r="M27" s="3"/>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1345,9 +1402,12 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1372,15 +1432,18 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>10</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M29" s="3"/>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N29" s="3"/>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1411,9 +1474,12 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-      <c r="M30" s="3"/>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3"/>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1444,75 +1510,84 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-      <c r="M31" s="3"/>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3"/>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-477000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-415000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>46000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>70000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-163000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-78000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-204000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-101000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>8000</v>
       </c>
-      <c r="M32" s="3"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>62360000</v>
+      </c>
+      <c r="E33" s="3">
         <v>39098000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>23200000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>39370000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>29146000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>18485000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>22112000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>15934000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>10188000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3669000</v>
       </c>
-      <c r="M33" s="3"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1543,80 +1618,89 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-      <c r="M34" s="3"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>62360000</v>
+      </c>
+      <c r="E35" s="3">
         <v>39098000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>23200000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>39370000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>29146000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>18485000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>22112000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>15934000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>10188000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3669000</v>
       </c>
-      <c r="M35" s="3"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1630,8 +1714,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1645,107 +1730,117 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>43889000</v>
+      </c>
+      <c r="E41" s="3">
         <v>41862000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>14681000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>16601000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>17576000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>19079000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>10019000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>8079000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8903000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4907000</v>
       </c>
-      <c r="M41" s="3"/>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N41" s="3"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>33926000</v>
+      </c>
+      <c r="E42" s="3">
         <v>23541000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>26057000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>31397000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>44378000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>35776000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>31095000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>33632000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>20546000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>13527000</v>
       </c>
-      <c r="M42" s="3"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>16994000</v>
+      </c>
+      <c r="E43" s="3">
         <v>16169000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>13466000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>14039000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>11335000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>9518000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7587000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5832000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3993000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2559000</v>
       </c>
-      <c r="M43" s="3"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3"/>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1770,15 +1865,18 @@
       <c r="J44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
       </c>
-      <c r="M44" s="3"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3"/>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1803,68 +1901,74 @@
       <c r="J45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L45" s="3">
         <v>959000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>659000</v>
       </c>
-      <c r="M45" s="3"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="3"/>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>100045000</v>
+      </c>
+      <c r="E46" s="3">
         <v>85365000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>59549000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>66666000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>75670000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>66225000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>50480000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>48563000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>34401000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>21652000</v>
       </c>
-      <c r="M46" s="3"/>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N46" s="3"/>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>6070000</v>
+      </c>
+      <c r="E47" s="3">
         <v>6141000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>6201000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>6775000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>6234000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>86000</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>10</v>
@@ -1875,75 +1979,84 @@
       <c r="L47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M47" s="3"/>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N47" s="3"/>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>136268000</v>
+      </c>
+      <c r="E48" s="3">
         <v>109881000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>92191000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>69964000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>54981000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>44783000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>24683000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>13721000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>8591000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5687000</v>
       </c>
-      <c r="M48" s="3"/>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="3"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>21569000</v>
+      </c>
+      <c r="E49" s="3">
         <v>21442000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>21203000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>19831000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>19673000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>19609000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>19595000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>20105000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>20657000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>21272000</v>
       </c>
-      <c r="M49" s="3"/>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1974,9 +2087,12 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-      <c r="M50" s="3"/>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2007,42 +2123,48 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-      <c r="M51" s="3"/>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>12102000</v>
+      </c>
+      <c r="E52" s="3">
         <v>6794000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>6583000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2751000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2758000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2673000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2576000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2135000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1312000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>796000</v>
       </c>
-      <c r="M52" s="3"/>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2073,42 +2195,48 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-      <c r="M53" s="3"/>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>276054000</v>
+      </c>
+      <c r="E54" s="3">
         <v>229623000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>185727000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>165987000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>159316000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>133376000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>97334000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>84524000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>64961000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>49407000</v>
       </c>
-      <c r="M54" s="3"/>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N54" s="3"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2122,8 +2250,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2137,161 +2266,174 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7687000</v>
+      </c>
+      <c r="E57" s="3">
         <v>4849000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4990000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4083000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1331000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1363000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>820000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>380000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>582000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>413000</v>
       </c>
-      <c r="M57" s="3"/>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1713000</v>
+        <v>2018000</v>
       </c>
       <c r="E58" s="3">
+        <v>1623000</v>
+      </c>
+      <c r="F58" s="3">
         <v>1367000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1127000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1023000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>800000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>500000</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>208000</v>
       </c>
-      <c r="M58" s="3"/>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3"/>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>18739000</v>
+        <v>17541000</v>
       </c>
       <c r="E59" s="3">
+        <v>18829000</v>
+      </c>
+      <c r="F59" s="3">
         <v>16078000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>12773000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>10018000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>11186000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4494000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2590000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2293000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1304000</v>
       </c>
-      <c r="M59" s="3"/>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N59" s="3"/>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>33596000</v>
+      </c>
+      <c r="E60" s="3">
         <v>31960000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>27026000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>21135000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>14981000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>15053000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7017000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3760000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2875000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1925000</v>
       </c>
-      <c r="M60" s="3"/>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N60" s="3"/>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>36211000</v>
+        <v>47751000</v>
       </c>
       <c r="E61" s="3">
+        <v>35611000</v>
+      </c>
+      <c r="F61" s="3">
         <v>25224000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>12746000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>9631000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>9524000</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -2299,44 +2441,50 @@
         <v>0</v>
       </c>
       <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>107000</v>
       </c>
-      <c r="M61" s="3"/>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3"/>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>8284000</v>
+        <v>12070000</v>
       </c>
       <c r="E62" s="3">
+        <v>8884000</v>
+      </c>
+      <c r="F62" s="3">
         <v>7764000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>7227000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>6414000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>7745000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5517000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>6367000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2892000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3157000</v>
       </c>
-      <c r="M62" s="3"/>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3"/>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2367,9 +2515,12 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-      <c r="M63" s="3"/>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2400,9 +2551,12 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-      <c r="M64" s="3"/>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3"/>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2433,42 +2587,48 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-      <c r="M65" s="3"/>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3"/>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>93417000</v>
+      </c>
+      <c r="E66" s="3">
         <v>76455000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>60014000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>41108000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>31026000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>32322000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>13207000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>10177000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5767000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5189000</v>
       </c>
-      <c r="M66" s="3"/>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N66" s="3"/>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2482,8 +2642,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2514,9 +2675,12 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-      <c r="M68" s="3"/>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3"/>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2547,9 +2711,12 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-      <c r="M69" s="3"/>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3"/>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2580,9 +2747,12 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-      <c r="M70" s="3"/>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3"/>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2613,42 +2783,48 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-      <c r="M71" s="3"/>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3"/>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>102506000</v>
+      </c>
+      <c r="E72" s="3">
         <v>82070000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>64799000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>69761000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>77345000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>55692000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>41981000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>33990000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>21670000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>9787000</v>
       </c>
-      <c r="M72" s="3"/>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N72" s="3"/>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2679,9 +2855,12 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-      <c r="M73" s="3"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3"/>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2712,9 +2891,12 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-      <c r="M74" s="3"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3"/>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2745,42 +2927,48 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-      <c r="M75" s="3"/>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3"/>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>182637000</v>
+      </c>
+      <c r="E76" s="3">
         <v>153168000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>125713000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>124879000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>128290000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>101054000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>84127000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>74347000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>59194000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>44218000</v>
       </c>
-      <c r="M76" s="3"/>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N76" s="3"/>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2811,80 +2999,89 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-      <c r="M77" s="3"/>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3"/>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2"/>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N80" s="2"/>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>62360000</v>
+      </c>
+      <c r="E81" s="3">
         <v>39098000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>23200000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>39370000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>29146000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>18485000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>22112000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>15934000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>10188000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3669000</v>
       </c>
-      <c r="M81" s="3"/>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3"/>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2898,41 +3095,45 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>15287000</v>
+      </c>
+      <c r="E83" s="3">
         <v>11017000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>8501000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>7560000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>6389000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5179000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3675000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2333000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2342000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1945000</v>
       </c>
-      <c r="M83" s="3"/>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3"/>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2963,9 +3164,12 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-      <c r="M84" s="3"/>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3"/>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2996,9 +3200,12 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-      <c r="M85" s="3"/>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3"/>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3029,9 +3236,12 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-      <c r="M86" s="3"/>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3"/>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3062,9 +3272,12 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-      <c r="M87" s="3"/>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3"/>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3095,42 +3308,48 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-      <c r="M88" s="3"/>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3"/>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>91328000</v>
+      </c>
+      <c r="E89" s="3">
         <v>71113000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>50475000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>57683000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>38747000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>36314000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>29274000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>24216000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>16108000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>10320000</v>
       </c>
-      <c r="M89" s="3"/>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N89" s="3"/>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3144,41 +3363,45 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-27266000</v>
+        <v>-37256000</v>
       </c>
       <c r="E91" s="3">
-        <v>-31431000</v>
+        <v>-27045000</v>
       </c>
       <c r="F91" s="3">
+        <v>-31186000</v>
+      </c>
+      <c r="G91" s="3">
         <v>-18690000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-15163000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-15102000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-13915000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-6733000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4491000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2523000</v>
       </c>
-      <c r="M91" s="3"/>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3"/>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3209,9 +3432,12 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-      <c r="M92" s="3"/>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3"/>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3242,42 +3468,48 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-      <c r="M93" s="3"/>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3"/>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-47150000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-24495000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-28970000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-7570000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-30059000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-19864000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-11603000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-20118000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-11792000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-9434000</v>
       </c>
-      <c r="M94" s="3"/>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="3"/>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3291,13 +3523,14 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>5072000</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
@@ -3323,9 +3556,12 @@
       <c r="L96" s="3">
         <v>0</v>
       </c>
-      <c r="M96" s="3"/>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3"/>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3356,9 +3592,12 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-      <c r="M97" s="3"/>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3"/>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3389,9 +3628,12 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-      <c r="M98" s="3"/>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3"/>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3422,106 +3664,118 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-      <c r="M99" s="3"/>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3"/>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-40781000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-19500000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-22136000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-50728000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-10292000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-7299000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-15572000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-5235000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-310000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-139000</v>
       </c>
-      <c r="M100" s="3"/>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N100" s="3"/>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-786000</v>
+      </c>
+      <c r="E101" s="3">
         <v>113000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-638000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-474000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>279000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>4000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-179000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>232000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-63000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-155000</v>
       </c>
-      <c r="M101" s="3"/>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3"/>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2611000</v>
+      </c>
+      <c r="E102" s="3">
         <v>27231000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1269000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1089000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1325000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>9155000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1920000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-905000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>3943000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>592000</v>
       </c>
-      <c r="M102" s="3"/>
+      <c r="N102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/META_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/META_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="92">
   <si>
     <t>META</t>
   </si>
@@ -656,173 +656,186 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>200966000</v>
+      </c>
+      <c r="E8" s="3">
         <v>164501000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>134902000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>116609000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>117929000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>85965000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>70697000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>55838000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>40653000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>27638000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>17928000</v>
       </c>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>30130000</v>
+        <v>36175000</v>
       </c>
       <c r="E9" s="3">
-        <v>26006000</v>
+        <v>30161000</v>
       </c>
       <c r="F9" s="3">
+        <v>25959000</v>
+      </c>
+      <c r="G9" s="3">
         <v>23754000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>22649000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>16692000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>12770000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>9355000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>5454000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3789000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2867000</v>
       </c>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>134371000</v>
+        <v>164791000</v>
       </c>
       <c r="E10" s="3">
-        <v>108896000</v>
+        <v>134340000</v>
       </c>
       <c r="F10" s="3">
+        <v>108943000</v>
+      </c>
+      <c r="G10" s="3">
         <v>92855000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>95280000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>69273000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>57927000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>46483000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>35199000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>23849000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>15061000</v>
       </c>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -837,44 +850,48 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>43619000</v>
+        <v>57372000</v>
       </c>
       <c r="E12" s="3">
-        <v>36911000</v>
+        <v>43873000</v>
       </c>
       <c r="F12" s="3">
+        <v>38483000</v>
+      </c>
+      <c r="G12" s="3">
         <v>33619000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>24655000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>18447000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>13600000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>10273000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>7754000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>5919000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>4816000</v>
       </c>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -908,32 +925,35 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>-1119000</v>
-      </c>
-      <c r="E14" s="3">
-        <v>2356000</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="3">
         <v>5058000</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J14" s="3">
         <v>5000000</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>10</v>
@@ -944,45 +964,51 @@
       <c r="M14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>15498000</v>
+        <v>18616000</v>
       </c>
       <c r="E15" s="3">
+        <v>15440000</v>
+      </c>
+      <c r="F15" s="3">
         <v>11178000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>8686000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>7967000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>6862000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>5741000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4315000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3025000</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -994,80 +1020,87 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>96282000</v>
+        <v>117690000</v>
       </c>
       <c r="E17" s="3">
-        <v>85896000</v>
+        <v>95121000</v>
       </c>
       <c r="F17" s="3">
+        <v>88151000</v>
+      </c>
+      <c r="G17" s="3">
         <v>83054000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>71176000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>53294000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>41711000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>30925000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>20450000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>15211000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>11703000</v>
       </c>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>68219000</v>
+        <v>83276000</v>
       </c>
       <c r="E18" s="3">
-        <v>49006000</v>
+        <v>69380000</v>
       </c>
       <c r="F18" s="3">
+        <v>46751000</v>
+      </c>
+      <c r="G18" s="3">
         <v>33555000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>46753000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>32671000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>28986000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>24913000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>20203000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>12427000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>6225000</v>
       </c>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1082,97 +1115,104 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>477000</v>
+        <v>-1698000</v>
       </c>
       <c r="E20" s="3">
-        <v>415000</v>
+        <v>519000</v>
       </c>
       <c r="F20" s="3">
+        <v>516000</v>
+      </c>
+      <c r="G20" s="3">
         <v>-46000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-70000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>163000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>78000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>204000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>101000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-8000</v>
       </c>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>83240000</v>
+        <v>103590000</v>
       </c>
       <c r="E21" s="3">
-        <v>59769000</v>
+        <v>84301000</v>
       </c>
       <c r="F21" s="3">
+        <v>57413000</v>
+      </c>
+      <c r="G21" s="3">
         <v>42287000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>54790000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>39370000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>34649000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>29024000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>23227000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>14870000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>8162000</v>
       </c>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1165000</v>
+      </c>
+      <c r="E22" s="3">
         <v>715000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>446000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>185000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>23000</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>10</v>
@@ -1180,90 +1220,99 @@
       <c r="J22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L22" s="3">
         <v>6000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>10000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>23000</v>
       </c>
-      <c r="N22" s="3"/>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3"/>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>85932000</v>
+      </c>
+      <c r="E23" s="3">
         <v>70663000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>47428000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>28819000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>47284000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>33180000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>24812000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>25361000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>20594000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>12518000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>6194000</v>
       </c>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>25474000</v>
+      </c>
+      <c r="E24" s="3">
         <v>8303000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>8330000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5619000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>7914000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4034000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>6327000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3249000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4660000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2301000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2506000</v>
       </c>
-      <c r="N24" s="3"/>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1297,81 +1346,90 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3"/>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>60458000</v>
+      </c>
+      <c r="E26" s="3">
         <v>62360000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>39098000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>23200000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>39370000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>29146000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>18485000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>22112000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>15934000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>10217000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3688000</v>
       </c>
-      <c r="N26" s="3"/>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3"/>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>60458000</v>
+      </c>
+      <c r="E27" s="3">
         <v>62360000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>39098000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>23200000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>39370000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>29146000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>18485000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>22111000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>15920000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>10188000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3669000</v>
       </c>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3"/>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1405,9 +1463,12 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-      <c r="N28" s="3"/>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3"/>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1435,15 +1496,18 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>10</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O29" s="3"/>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1477,9 +1541,12 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-      <c r="N30" s="3"/>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3"/>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1513,81 +1580,90 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-      <c r="N31" s="3"/>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3"/>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-477000</v>
+        <v>1698000</v>
       </c>
       <c r="E32" s="3">
-        <v>-415000</v>
+        <v>-519000</v>
       </c>
       <c r="F32" s="3">
+        <v>-516000</v>
+      </c>
+      <c r="G32" s="3">
         <v>46000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>70000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-163000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-78000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-204000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-101000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>8000</v>
       </c>
-      <c r="N32" s="3"/>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3"/>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>60458000</v>
+      </c>
+      <c r="E33" s="3">
         <v>62360000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>39098000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>23200000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>39370000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>29146000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>18485000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>22112000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>15934000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>10188000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3669000</v>
       </c>
-      <c r="N33" s="3"/>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1621,86 +1697,95 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-      <c r="N34" s="3"/>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>60458000</v>
+      </c>
+      <c r="E35" s="3">
         <v>62360000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>39098000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>23200000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>39370000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>29146000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>18485000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>22112000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>15934000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>10188000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3669000</v>
       </c>
-      <c r="N35" s="3"/>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O38" s="2"/>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1715,8 +1800,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1731,116 +1817,126 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>35873000</v>
+      </c>
+      <c r="E41" s="3">
         <v>43889000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>41862000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>14681000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>16601000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>17576000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>19079000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>10019000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8079000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8903000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4907000</v>
       </c>
-      <c r="N41" s="3"/>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3"/>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>45719000</v>
+      </c>
+      <c r="E42" s="3">
         <v>33926000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>23541000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>26057000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>31397000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>44378000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>35776000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>31095000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>33632000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>20546000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>13527000</v>
       </c>
-      <c r="N42" s="3"/>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>19769000</v>
+      </c>
+      <c r="E43" s="3">
         <v>16994000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>16169000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>13466000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>14039000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>11335000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>9518000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>7587000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5832000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3993000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2559000</v>
       </c>
-      <c r="N43" s="3"/>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3"/>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1868,15 +1964,18 @@
       <c r="K44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
       </c>
-      <c r="N44" s="3"/>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+      <c r="O44" s="3"/>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1904,74 +2003,80 @@
       <c r="K45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M45" s="3">
         <v>959000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>659000</v>
       </c>
-      <c r="N45" s="3"/>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>108722000</v>
+      </c>
+      <c r="E46" s="3">
         <v>100045000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>85365000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>59549000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>66666000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>75670000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>66225000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>50480000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>48563000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>34401000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>21652000</v>
       </c>
-      <c r="N46" s="3"/>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3"/>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>27524000</v>
+      </c>
+      <c r="E47" s="3">
         <v>6070000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>6141000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>6201000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>6775000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>6234000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>86000</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>10</v>
@@ -1982,81 +2087,90 @@
       <c r="M47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N47" s="3"/>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O47" s="3"/>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>196804000</v>
+      </c>
+      <c r="E48" s="3">
         <v>136268000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>109881000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>92191000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>69964000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>54981000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>44783000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>24683000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>13721000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8591000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5687000</v>
       </c>
-      <c r="N48" s="3"/>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3"/>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>28226000</v>
+      </c>
+      <c r="E49" s="3">
         <v>21569000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>21442000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>21203000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>19831000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>19673000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>19609000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>19595000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>20105000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>20657000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>21272000</v>
       </c>
-      <c r="N49" s="3"/>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3"/>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2090,9 +2204,12 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-      <c r="N50" s="3"/>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3"/>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2126,45 +2243,51 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-      <c r="N51" s="3"/>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3"/>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4745000</v>
+      </c>
+      <c r="E52" s="3">
         <v>12102000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>6794000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>6583000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2751000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2758000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2673000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2576000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2135000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1312000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>796000</v>
       </c>
-      <c r="N52" s="3"/>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3"/>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2198,45 +2321,51 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-      <c r="N53" s="3"/>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3"/>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>366021000</v>
+      </c>
+      <c r="E54" s="3">
         <v>276054000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>229623000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>185727000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>165987000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>159316000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>133376000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>97334000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>84524000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>64961000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>49407000</v>
       </c>
-      <c r="N54" s="3"/>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O54" s="3"/>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2251,8 +2380,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2267,176 +2397,189 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8894000</v>
+      </c>
+      <c r="E57" s="3">
         <v>7687000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4849000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4990000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4083000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1331000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1363000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>820000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>380000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>582000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>413000</v>
       </c>
-      <c r="N57" s="3"/>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3"/>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2018000</v>
+        <v>2521000</v>
       </c>
       <c r="E58" s="3">
+        <v>1942000</v>
+      </c>
+      <c r="F58" s="3">
         <v>1623000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1367000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1127000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1023000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>800000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>500000</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>208000</v>
       </c>
-      <c r="N58" s="3"/>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3"/>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>17541000</v>
+        <v>23270000</v>
       </c>
       <c r="E59" s="3">
+        <v>17617000</v>
+      </c>
+      <c r="F59" s="3">
         <v>18829000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>16078000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>12773000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>10018000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>11186000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4494000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2590000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2293000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1304000</v>
       </c>
-      <c r="N59" s="3"/>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3"/>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>41836000</v>
+      </c>
+      <c r="E60" s="3">
         <v>33596000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>31960000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>27026000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>21135000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>14981000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>15053000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7017000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3760000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2875000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1925000</v>
       </c>
-      <c r="N60" s="3"/>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="3"/>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>47751000</v>
+        <v>82560000</v>
       </c>
       <c r="E61" s="3">
+        <v>47118000</v>
+      </c>
+      <c r="F61" s="3">
         <v>35611000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>25224000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>12746000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>9631000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>9524000</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -2444,47 +2587,53 @@
         <v>0</v>
       </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>107000</v>
       </c>
-      <c r="N61" s="3"/>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3"/>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>12070000</v>
+        <v>24382000</v>
       </c>
       <c r="E62" s="3">
+        <v>12703000</v>
+      </c>
+      <c r="F62" s="3">
         <v>8884000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>7764000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>7227000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>6414000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>7745000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5517000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6367000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2892000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3157000</v>
       </c>
-      <c r="N62" s="3"/>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3"/>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2518,9 +2667,12 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-      <c r="N63" s="3"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3"/>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2554,9 +2706,12 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-      <c r="N64" s="3"/>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3"/>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2590,45 +2745,51 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-      <c r="N65" s="3"/>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3"/>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>148778000</v>
+      </c>
+      <c r="E66" s="3">
         <v>93417000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>76455000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>60014000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>41108000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>31026000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>32322000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>13207000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>10177000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5767000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5189000</v>
       </c>
-      <c r="N66" s="3"/>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O66" s="3"/>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2643,8 +2804,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2678,9 +2840,12 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-      <c r="N68" s="3"/>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3"/>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2714,9 +2879,12 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-      <c r="N69" s="3"/>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3"/>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2750,9 +2918,12 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-      <c r="N70" s="3"/>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3"/>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2786,45 +2957,51 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-      <c r="N71" s="3"/>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3"/>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>121179000</v>
+      </c>
+      <c r="E72" s="3">
         <v>102506000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>82070000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>64799000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>69761000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>77345000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>55692000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>41981000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>33990000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>21670000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>9787000</v>
       </c>
-      <c r="N72" s="3"/>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3"/>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2858,9 +3035,12 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-      <c r="N73" s="3"/>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3"/>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2894,9 +3074,12 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-      <c r="N74" s="3"/>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3"/>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2930,45 +3113,51 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-      <c r="N75" s="3"/>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3"/>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>217243000</v>
+      </c>
+      <c r="E76" s="3">
         <v>182637000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>153168000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>125713000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>124879000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>128290000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>101054000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>84127000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>74347000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>59194000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>44218000</v>
       </c>
-      <c r="N76" s="3"/>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O76" s="3"/>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3002,86 +3191,95 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-      <c r="N77" s="3"/>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3"/>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2"/>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O80" s="2"/>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>60458000</v>
+      </c>
+      <c r="E81" s="3">
         <v>62360000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>39098000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>23200000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>39370000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>29146000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>18485000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>22112000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>15934000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>10188000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3669000</v>
       </c>
-      <c r="N81" s="3"/>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3"/>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3096,44 +3294,48 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>18001000</v>
+      </c>
+      <c r="E83" s="3">
         <v>15287000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>11017000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>8501000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>7560000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>6389000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>5179000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3675000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2333000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2342000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1945000</v>
       </c>
-      <c r="N83" s="3"/>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3"/>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3167,9 +3369,12 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-      <c r="N84" s="3"/>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3"/>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3203,9 +3408,12 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-      <c r="N85" s="3"/>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3"/>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3239,9 +3447,12 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-      <c r="N86" s="3"/>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3"/>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3275,9 +3486,12 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-      <c r="N87" s="3"/>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3"/>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3311,45 +3525,51 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-      <c r="N88" s="3"/>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3"/>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>115800000</v>
+      </c>
+      <c r="E89" s="3">
         <v>91328000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>71113000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>50475000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>57683000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>38747000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>36314000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>29274000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>24216000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>16108000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>10320000</v>
       </c>
-      <c r="N89" s="3"/>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3"/>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3364,44 +3584,48 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-69691000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-37256000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-27045000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-31186000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-18690000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-15163000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-15102000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-13915000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-6733000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4491000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2523000</v>
       </c>
-      <c r="N91" s="3"/>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3"/>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3435,9 +3659,12 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-      <c r="N92" s="3"/>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3"/>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3471,45 +3698,51 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-      <c r="N93" s="3"/>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3"/>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-102003000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-47150000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-24495000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-28970000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-7570000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-30059000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-19864000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-11603000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-20118000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-11792000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-9434000</v>
       </c>
-      <c r="N94" s="3"/>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3"/>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3524,17 +3757,18 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>5324000</v>
+      </c>
+      <c r="E96" s="3">
         <v>5072000</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
@@ -3559,9 +3793,12 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-      <c r="N96" s="3"/>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3"/>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3595,9 +3832,12 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-      <c r="N97" s="3"/>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3"/>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3631,9 +3871,12 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-      <c r="N98" s="3"/>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3"/>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3667,115 +3910,127 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-      <c r="N99" s="3"/>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3"/>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-20370000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-40781000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-19500000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-22136000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-50728000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-10292000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-7299000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-15572000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-5235000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-310000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-139000</v>
       </c>
-      <c r="N100" s="3"/>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3"/>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>235000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-786000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>113000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-638000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-474000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>279000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>4000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-179000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>232000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-63000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-155000</v>
       </c>
-      <c r="N101" s="3"/>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3"/>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-6338000</v>
+      </c>
+      <c r="E102" s="3">
         <v>2611000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>27231000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1269000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1089000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1325000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>9155000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1920000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-905000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>3943000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>592000</v>
       </c>
-      <c r="N102" s="3"/>
+      <c r="O102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/META_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/META_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="92">
   <si>
     <t>META</t>
   </si>
@@ -934,14 +934,14 @@
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>10</v>
+      <c r="D14" s="3">
+        <v>-1138000</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-53000</v>
+      </c>
+      <c r="F14" s="3">
+        <v>102000</v>
       </c>
       <c r="G14" s="3">
         <v>5058000</v>
@@ -1122,13 +1122,13 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-1698000</v>
+        <v>-560000</v>
       </c>
       <c r="E20" s="3">
-        <v>519000</v>
+        <v>572000</v>
       </c>
       <c r="F20" s="3">
-        <v>516000</v>
+        <v>414000</v>
       </c>
       <c r="G20" s="3">
         <v>-46000</v>
@@ -1161,13 +1161,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>103590000</v>
+        <v>102452000</v>
       </c>
       <c r="E21" s="3">
-        <v>84301000</v>
+        <v>84248000</v>
       </c>
       <c r="F21" s="3">
-        <v>57413000</v>
+        <v>57515000</v>
       </c>
       <c r="G21" s="3">
         <v>42287000</v>
@@ -1590,13 +1590,13 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>1698000</v>
+        <v>560000</v>
       </c>
       <c r="E32" s="3">
-        <v>-519000</v>
+        <v>-572000</v>
       </c>
       <c r="F32" s="3">
-        <v>-516000</v>
+        <v>-414000</v>
       </c>
       <c r="G32" s="3">
         <v>46000</v>
